--- a/textbook_examples/mod01_lookup.xlsx
+++ b/textbook_examples/mod01_lookup.xlsx
@@ -580,7 +580,7 @@
         <v>41.2</v>
       </c>
       <c r="E5" s="9">
-        <f>XLOOKUP(B5,$H$5:$H$7,$I$5:$I$7)</f>
+        <f>_xlfn.XLOOKUP(B5,$H$5:$H$7,$I$5:$I$7)</f>
         <v/>
       </c>
       <c r="F5" s="10">
@@ -614,7 +614,7 @@
         <v>58.6</v>
       </c>
       <c r="E6" s="9">
-        <f>XLOOKUP(B6,$H$5:$H$7,$I$5:$I$7)</f>
+        <f>_xlfn.XLOOKUP(B6,$H$5:$H$7,$I$5:$I$7)</f>
         <v/>
       </c>
       <c r="F6" s="10">
@@ -648,7 +648,7 @@
         <v>37.9</v>
       </c>
       <c r="E7" s="9">
-        <f>XLOOKUP(B7,$H$5:$H$7,$I$5:$I$7)</f>
+        <f>_xlfn.XLOOKUP(B7,$H$5:$H$7,$I$5:$I$7)</f>
         <v/>
       </c>
       <c r="F7" s="10">
@@ -682,7 +682,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="E8" s="9">
-        <f>XLOOKUP(B8,$H$5:$H$7,$I$5:$I$7)</f>
+        <f>_xlfn.XLOOKUP(B8,$H$5:$H$7,$I$5:$I$7)</f>
         <v/>
       </c>
       <c r="F8" s="10">
@@ -708,7 +708,7 @@
         <v>61.3</v>
       </c>
       <c r="E9" s="9">
-        <f>XLOOKUP(B9,$H$5:$H$7,$I$5:$I$7)</f>
+        <f>_xlfn.XLOOKUP(B9,$H$5:$H$7,$I$5:$I$7)</f>
         <v/>
       </c>
       <c r="F9" s="10">
@@ -734,7 +734,7 @@
         <v>44.8</v>
       </c>
       <c r="E10" s="9">
-        <f>XLOOKUP(B10,$H$5:$H$7,$I$5:$I$7)</f>
+        <f>_xlfn.XLOOKUP(B10,$H$5:$H$7,$I$5:$I$7)</f>
         <v/>
       </c>
       <c r="F10" s="10">
@@ -760,7 +760,7 @@
         <v>68.09999999999999</v>
       </c>
       <c r="E11" s="9">
-        <f>XLOOKUP(B11,$H$5:$H$7,$I$5:$I$7)</f>
+        <f>_xlfn.XLOOKUP(B11,$H$5:$H$7,$I$5:$I$7)</f>
         <v/>
       </c>
       <c r="F11" s="10">
@@ -786,7 +786,7 @@
         <v>55.2</v>
       </c>
       <c r="E12" s="9">
-        <f>XLOOKUP(B12,$H$5:$H$7,$I$5:$I$7)</f>
+        <f>_xlfn.XLOOKUP(B12,$H$5:$H$7,$I$5:$I$7)</f>
         <v/>
       </c>
       <c r="F12" s="10">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>XLOOKUP(B5,$H$5:$H$7,$I$5:$I$7)</f>
+        <f>_xlfn.XLOOKUP(B5,$H$5:$H$7,$I$5:$I$7)</f>
         <v/>
       </c>
       <c r="C15" s="10">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B18" s="6">
-        <f>XLOOKUP("Lentils",$H$5:$H$7,$I$5:$I$7,"no price")</f>
+        <f>_xlfn.XLOOKUP("Lentils",$H$5:$H$7,$I$5:$I$7,"no price")</f>
         <v/>
       </c>
       <c r="C18" s="10">

--- a/textbook_examples/mod01_lookup.xlsx
+++ b/textbook_examples/mod01_lookup.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaskca1-my.sharepoint.com/personal/pjs998_usask_ca/Documents/Teaching/261/2026/textbook_261/textbook_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_77FD4CEAFB7C18758FB7D93929CBB3AC6B5D6459" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD6CC07C-E66C-1349-89ED-653C5095797E}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="11_77FD4CEAFB7C18758FB7D93929CBB3AC6B5D6459" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1094EA1F-A308-EB49-B010-3EC636D59469}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Completed" sheetId="1" r:id="rId1"/>
-    <sheet name="Incomplete" sheetId="3" r:id="rId2"/>
+    <sheet name="Practice" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
